--- a/Result/profitability/3016.xlsx
+++ b/Result/profitability/3016.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.08499999999999996</v>
+        <v>0.14625</v>
       </c>
       <c r="N2" t="n">
-        <v>8.800000000000001</v>
+        <v>10.46125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06999999999999997</v>
+        <v>0.13875</v>
       </c>
       <c r="N3" t="n">
-        <v>8.9</v>
+        <v>10.89875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -901,13 +901,13 @@
         <v>0.06</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06499999999999997</v>
+        <v>0.145</v>
       </c>
       <c r="N4" t="n">
-        <v>7.93</v>
+        <v>10.0725</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1020,10 +1020,10 @@
         <v>-0.66</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.01875000000000003</v>
+        <v>0.08124999999999996</v>
       </c>
       <c r="N5" t="n">
-        <v>5.069999999999999</v>
+        <v>7.37125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>-0.52</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.06500000000000003</v>
+        <v>0.009999999999999967</v>
       </c>
       <c r="N6" t="n">
-        <v>0.09124999999999961</v>
+        <v>2.04875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1268,13 +1268,13 @@
         <v>-0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.07500000000000004</v>
+        <v>-0.01375000000000003</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7212500000000001</v>
+        <v>0.7337500000000002</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1286,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>-0.16</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.115</v>
+        <v>-0.07750000000000003</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.01375</v>
+        <v>-1.30375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1652,7 +1652,7 @@
         <v>-0.175</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.141249999999999</v>
+        <v>-3.14125</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1779,7 +1779,7 @@
         <v>-0.145</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.021249999999999</v>
+        <v>-2.02125</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1906,7 +1906,7 @@
         <v>-0.1075</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4512500000000008</v>
+        <v>0.4512500000000004</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2030,10 +2030,10 @@
         <v>0.13</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.008750000000000029</v>
+        <v>-0.008750000000000022</v>
       </c>
       <c r="N13" t="n">
-        <v>4.628750000000001</v>
+        <v>4.62875</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3016</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1309</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1002</v>
+      </c>
+      <c r="E75" t="n">
+        <v>307</v>
+      </c>
+      <c r="F75" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="G75" t="n">
+        <v>221</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>16.92%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>229</v>
+      </c>
+      <c r="K75" t="n">
+        <v>188</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.16625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>11.22375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.8571428571428574</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3196398424310636</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-5.333333333333334</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>3.652777777777778</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
